--- a/public/Rutas.xlsx
+++ b/public/Rutas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\reportes mensuales\varios\Proyecto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6807355A-7580-4D49-B797-1A7FEF2BE6D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C259CB-30F5-4878-89C3-CAFE9C2BADFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
   <si>
     <t>DATOS</t>
   </si>
@@ -240,6 +240,90 @@
   </si>
   <si>
     <t>SAN FRANCISCO EL ALTO</t>
+  </si>
+  <si>
+    <t>TEJUTLA</t>
+  </si>
+  <si>
+    <t>TAJUMULCO</t>
+  </si>
+  <si>
+    <t>SAN PEDRO</t>
+  </si>
+  <si>
+    <t>CATARINA</t>
+  </si>
+  <si>
+    <t>EL QUETZAL</t>
+  </si>
+  <si>
+    <t>LA REFORMA</t>
+  </si>
+  <si>
+    <t>GENOVA</t>
+  </si>
+  <si>
+    <t>FLORES COSTA CUCA</t>
+  </si>
+  <si>
+    <t>SAN SEBASTIAN</t>
+  </si>
+  <si>
+    <t>SAN MARTIN</t>
+  </si>
+  <si>
+    <t>SAN MARTIN ZAPOTITLAN</t>
+  </si>
+  <si>
+    <t>SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>SAN MIGUEL PANAM</t>
+  </si>
+  <si>
+    <t>LA BLANCA</t>
+  </si>
+  <si>
+    <t>SANTA MARIA CHIQUIMULA</t>
+  </si>
+  <si>
+    <t>SAN JUAN OSTUNCALCO</t>
+  </si>
+  <si>
+    <t>JACALTENANGO</t>
+  </si>
+  <si>
+    <t>LA MESILLA</t>
+  </si>
+  <si>
+    <t>SANTA ANA HUISTA</t>
+  </si>
+  <si>
+    <t>SAN ANTONIO HUISTA</t>
+  </si>
+  <si>
+    <t>NENTON</t>
+  </si>
+  <si>
+    <t>BARILLAS</t>
+  </si>
+  <si>
+    <t>SAN MATEO IXTATAN</t>
+  </si>
+  <si>
+    <t>SAN SEBASTIAN COATAN</t>
+  </si>
+  <si>
+    <t>TODOS SANTOS</t>
+  </si>
+  <si>
+    <t>SAN LUCAS TOLIMAN</t>
+  </si>
+  <si>
+    <t>MALACATANCITO</t>
+  </si>
+  <si>
+    <t>SANTA LUCIA LA REFORMA</t>
   </si>
 </sst>
 </file>
@@ -288,7 +372,57 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -313,8 +447,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{305ACA8E-3D51-4E88-85F0-DCFD169D6B87}" name="Tabla2" displayName="Tabla2" ref="A1:A68" totalsRowShown="0">
-  <autoFilter ref="A1:A68" xr:uid="{305ACA8E-3D51-4E88-85F0-DCFD169D6B87}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{305ACA8E-3D51-4E88-85F0-DCFD169D6B87}" name="Tabla2" displayName="Tabla2" ref="A1:A96" totalsRowShown="0">
+  <autoFilter ref="A1:A96" xr:uid="{305ACA8E-3D51-4E88-85F0-DCFD169D6B87}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{8CDC6BF8-B248-4EAA-A32A-E785AC15F71A}" name="DATOS"/>
   </tableColumns>
@@ -585,7 +719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A68"/>
+  <dimension ref="A1:A96"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.7109375" customWidth="1"/>
@@ -932,9 +1066,153 @@
         <v>67</v>
       </c>
     </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>95</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A49:A1048576 A1:A47">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
